--- a/assets/xls/基础类型.xlsx
+++ b/assets/xls/基础类型.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21315" windowHeight="10680" tabRatio="535"/>
+    <workbookView windowWidth="21555" windowHeight="11265" tabRatio="535"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Count</t>
+    <t>Amount</t>
   </si>
   <si>
     <t>int32</t>

--- a/assets/xls/基础类型.xlsx
+++ b/assets/xls/基础类型.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21555" windowHeight="11265" tabRatio="535"/>
+    <workbookView windowWidth="19548" windowHeight="9780" tabRatio="535" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="7" r:id="rId1"/>
+    <sheet name="Attribute" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resource!$A$4:$B$4</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>ID</t>
   </si>
@@ -49,6 +50,18 @@
   </si>
   <si>
     <t>数量</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>AttributeType</t>
+  </si>
+  <si>
+    <t>属性ID</t>
+  </si>
+  <si>
+    <t>属性数值</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1052,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="15.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.375" style="2" customWidth="1"/>
@@ -1082,4 +1095,52 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="9.9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>